--- a/data/trans_bre/P44D-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P44D-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 12,28</t>
+          <t>-19,53; 12,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 5,06</t>
+          <t>-3,02; 4,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-79,16; —</t>
+          <t>-74,02; —</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>-1,62</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>120,59%</t>
+          <t>-23,71%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 16,07</t>
+          <t>-27,18; 16,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 18,74</t>
+          <t>-16,99; 20,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 8,92</t>
+          <t>-6,53; 3,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,05; 277,18</t>
+          <t>-80,33; 280,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 1138,36</t>
+          <t>-64,8; 105,29</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-16,66%</t>
+          <t>-14,71%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 43,83</t>
+          <t>-2,04; 40,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 29,34</t>
+          <t>-11,56; 29,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 5,61</t>
+          <t>-10,73; 6,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,26; 55,53</t>
+          <t>-56,79; 57,44</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>-4,65</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-32,41%</t>
+          <t>-35,99%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 29,42</t>
+          <t>-19,09; 27,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 8,07</t>
+          <t>-25,33; 7,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 0,7</t>
+          <t>-9,35; 0,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,04; 317,4</t>
+          <t>-71,78; 294,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-87,85; 60,42</t>
+          <t>-88,38; 57,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,4; 7,58</t>
+          <t>-59,07; 12,09</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>-2,56</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>-26,02%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 16,28</t>
+          <t>-5,21; 16,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 5,69</t>
+          <t>-11,34; 6,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 5,77</t>
+          <t>-5,35; 0,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-35,66; 218,21</t>
+          <t>-32,65; 213,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-62,29; 61,65</t>
+          <t>-64,23; 66,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 186,95</t>
+          <t>-46,64; 1,34</t>
         </is>
       </c>
     </row>
